--- a/questionnaire_templates/038_job_opportunity_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/038_job_opportunity_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'role1',_'label':_'role1',_'value':_'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'role1', 'label': 'role1', 'value': 'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'role2',_'label':_'role2',_'value':_'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'role2', 'label': 'role2', 'value': 'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'role3',_'label':_'role3',_'value':_'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'role3', 'label': 'role3', 'value': 'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'role4',_'label':_'role4',_'value':_'role4'}</t>
+          <t>role4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'role4', 'label': 'role4', 'value': 'role4'}</t>
+          <t>role4</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'role5',_'label':_'role5',_'value':_'role5'}</t>
+          <t>role5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'role5', 'label': 'role5', 'value': 'role5'}</t>
+          <t>role5</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'role1',_'label':_'role1',_'value':_'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'role1', 'label': 'role1', 'value': 'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'role2',_'label':_'role2',_'value':_'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'role2', 'label': 'role2', 'value': 'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'role3',_'label':_'role3',_'value':_'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'role3', 'label': 'role3', 'value': 'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'role1',_'label':_'role1',_'value':_'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'role1', 'label': 'role1', 'value': 'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'role2',_'label':_'role2',_'value':_'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'role2', 'label': 'role2', 'value': 'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'role3',_'label':_'role3',_'value':_'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'role3', 'label': 'role3', 'value': 'role3'}</t>
+          <t>role3</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'role4',_'label':_'role4',_'value':_'role4'}</t>
+          <t>role4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'role4', 'label': 'role4', 'value': 'role4'}</t>
+          <t>role4</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'role5',_'label':_'role5',_'value':_'role5'}</t>
+          <t>role5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'role5', 'label': 'role5', 'value': 'role5'}</t>
+          <t>role5</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'role1',_'label':_'role1',_'value':_'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'role1', 'label': 'role1', 'value': 'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'role2',_'label':_'role2',_'value':_'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'role2', 'label': 'role2', 'value': 'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_37,_'name':_'role1',_'label':_'role1',_'value':_'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 37, 'name': 'role1', 'label': 'role1', 'value': 'role1'}</t>
+          <t>role1</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_38,_'name':_'role2',_'label':_'role2',_'value':_'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 38, 'name': 'role2', 'label': 'role2', 'value': 'role2'}</t>
+          <t>role2</t>
         </is>
       </c>
     </row>
